--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>representedCustodianOrganization contient les éléments caractérisant la structure conservant le 
-document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
+    <t>representedCustodianOrganization contient les éléments caractérisant la structure conservant le document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>CustodianOrganization.typeId.nullFlavor</t>
@@ -1286,7 +1290,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1294,10 +1298,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1395,17 +1399,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1423,11 +1427,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1478,7 +1482,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1498,17 +1502,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1526,11 +1530,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1581,7 +1585,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1601,17 +1605,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1629,11 +1633,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1684,7 +1688,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1704,17 +1708,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1732,11 +1736,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1787,7 +1791,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1807,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1837,7 +1841,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1888,7 +1892,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1908,10 +1912,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1967,7 +1971,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1985,7 +1989,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2005,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2042,7 +2046,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2064,7 +2068,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2082,7 +2086,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2102,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2181,7 +2185,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2201,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2227,7 +2231,7 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2280,7 +2284,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2300,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2326,7 +2330,7 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2379,7 +2383,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2399,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2425,7 +2429,7 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2478,7 +2482,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2498,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2524,7 +2528,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2577,7 +2581,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="149">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -413,6 +413,36 @@
     <t>CustodianOrganization.id</t>
   </si>
   <si>
+    <t>Identifiant de la structure.</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.displayable</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.root</t>
+  </si>
+  <si>
+    <t>- Pour une structure sanitaire ou médico-sociale : valeur fixée à '1.2.250.1.71.4.2.2' 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : 
+valeur fixée à '1.2.250.1.213.4.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.extension</t>
+  </si>
+  <si>
+    <t>- Pour une structure sanitaire ou médico-sociale : valeur de Struct_idNat (voir annexe [6]) 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : Non renseigné</t>
+  </si>
+  <si>
     <t>CustodianOrganization.name</t>
   </si>
   <si>
@@ -420,6 +450,11 @@
 </t>
   </si>
   <si>
+    <t>Nom de la structure : 
+- Pour une structure sanitaire ou médico-sociale : valeur de Struct_Nom (voir annexe [6]) 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : valeur fixée à 'DMP'</t>
+  </si>
+  <si>
     <t>CustodianOrganization.telecom</t>
   </si>
   <si>
@@ -427,6 +462,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom de la structure.</t>
+  </si>
+  <si>
     <t>CustodianOrganization.sdtcTelecom</t>
   </si>
   <si>
@@ -435,6 +473,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
 </t>
+  </si>
+  <si>
+    <t>Adresse géopostale de la structure.</t>
   </si>
 </sst>
 </file>
@@ -736,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.55859375" customWidth="true" bestFit="true"/>
@@ -2134,7 +2175,9 @@
       <c r="K14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2205,16 +2248,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2231,10 +2276,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2260,13 +2307,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2284,7 +2329,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2313,7 +2358,9 @@
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
@@ -2330,10 +2377,12 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2383,7 +2432,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2403,21 +2452,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2429,10 +2480,12 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="M17" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2482,13 +2535,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2502,16 +2555,18 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
@@ -2528,10 +2583,14 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2581,7 +2640,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2596,6 +2655,513 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>representedCustodianOrganization contient les éléments caractérisant la structure conservant le document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
+    <t>L'élément de l'en-tête du CDA representedCustodianOrganization contient les éléments caractérisant la structure conservant le document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
